--- a/campanhas/pedido-cliente-novo-2026-07/selecao-cliente-novo-europa.xlsx
+++ b/campanhas/pedido-cliente-novo-2026-07/selecao-cliente-novo-europa.xlsx
@@ -101,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,12 +109,33 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -481,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -492,10 +513,11 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -539,6 +561,11 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Observacao</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Premiacoes / Pontuacoes</t>
         </is>
       </c>
     </row>
@@ -589,6 +616,11 @@
           <t>Estoque proprio: 1un</t>
         </is>
       </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Sem pontuacao/premiacao encontrada</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -630,6 +662,11 @@
           <t>Estoque proprio: 6un</t>
         </is>
       </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Sem pontuacao/premiacao encontrada</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -671,6 +708,11 @@
           <t>Estoque proprio: 3un</t>
         </is>
       </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Sem pontuacao da safra 2021; James Suckling avaliou a safra 2022 (nota nao disponivel publicamente)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -712,6 +754,11 @@
           <t>Estoque proprio: 1un</t>
         </is>
       </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>93pts Wine Spectator | 93pts James Suckling | 93pts Decanter | 92pts Jeb Dunnuck | 90pts Robert Parker</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -753,6 +800,11 @@
           <t>Estoque proprio: 1un</t>
         </is>
       </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>94pts James Suckling | 93pts Decanter | 92pts Vinous | 16,5/20 Jancis Robinson</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -794,6 +846,11 @@
           <t>Estoque proprio: 1un (tb no catalogo Tanyno)</t>
         </is>
       </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Sem nota da safra 2021 (lancamento recente); safras 2017-2018 do mesmo rotulo pontuaram 92-94pts (Wine Enthusiast / James Suckling)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -835,6 +892,11 @@
           <t>Estoque proprio: 1un</t>
         </is>
       </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Sem nota numerica confirmada da safra 2019; safra 2021 recebeu 96pts James Suckling</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -876,6 +938,11 @@
           <t>Estoque proprio: 1un</t>
         </is>
       </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>93pts Wine Spectator | 93pts Wine Advocate (Monica Larner) | 94pts Vinous (Eric Guido) | 94pts Jeb Dunnuck | 91pts James Suckling</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -917,1114 +984,1259 @@
           <t>Estoque proprio: 2un</t>
         </is>
       </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>94pts James Suckling (bottling Domaine du Pavillon / Clos des Ursulines, monopole da Albert Bichot)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Aluigi Chianti Classico Gran Selezione</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Le Cinciole</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>Sob consulta</t>
         </is>
       </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>96pts Vinous | 96pts Decanter | 93pts James Suckling / Wine Enthusiast / Wine Spectator | 92pts Falstaff</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Beaujolais Magnum</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Mee Godard</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="7" t="n">
         <v>606</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="7" t="n">
         <v>606</v>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>Sob consulta</t>
         </is>
       </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Sem pontuacao especifica encontrada pra essa cuvee em formato Magnum</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Mercurey 1er Cru Clos des Barraults</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Michel Juillot</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="7" t="n">
         <v>611</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="7" t="n">
         <v>611</v>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>Sob consulta</t>
         </is>
       </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Sem nota da safra 2023; safra 2015 do mesmo rotulo recebeu 89pts Wine Spectator</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Aloxe-Corton</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Dubreuil-Fontaine</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="7" t="n">
         <v>647</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="7" t="n">
         <v>647</v>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>Estoque Tanyno: 17un</t>
         </is>
       </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Sem pontuacao de critico nomeado encontrada (media agregada Wine-Searcher ~89pts)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Chateau Haut Bergey</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Chateau Haut Bergey</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>2005</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="7" t="n">
         <v>647</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="7" t="n">
         <v>647</v>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>Sob consulta</t>
         </is>
       </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>92pts Robert Parker/Wine Advocate | 91pts Wine Spectator | 90pts Vinous (Stephen Tanzer)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Barolo DOCG Riva Rocca</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Alario Claudio</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="7" t="n">
         <v>655</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="7" t="n">
         <v>655</v>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>Mesmo rotulo do Site (comparar estoque)</t>
         </is>
       </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>Sem nota da safra 2021 (lancamento recente); safras 2017-2018 do mesmo rotulo pontuaram 92-94pts (Wine Enthusiast / James Suckling)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Rosso di Montalcino DOC</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Cupano</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="7" t="n">
         <v>659</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="7" t="n">
         <v>659</v>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>Estoque Tanyno: 13un</t>
         </is>
       </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Sem premiacao encontrada especificamente pro Rosso (so ha notas do Brunello do mesmo produtor)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Pommard Les Vaumuriens</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Chantal Lescure</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="7" t="n">
         <v>665</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" s="7" t="n">
         <v>665</v>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>Estoque Tanyno: 1un</t>
         </is>
       </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>Sem nota individual de critico nomeado; media agregada Wine-Searcher ~91pts</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Boscarelli IGT Toscana</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Boscarelli</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="7" t="n">
         <v>676</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="7" t="n">
         <v>676</v>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>Sob consulta</t>
         </is>
       </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>Sem nota individual de critico nomeado; media agregada Wine-Searcher ~90pts</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Brunello di Montalcino Cielo D'Ulisse</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Podere Le Ripi</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="7" t="n">
         <v>682</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="7" t="n">
         <v>682</v>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>Sob consulta</t>
         </is>
       </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>93pts Wine Spectator | 94pts Vinous/Ian D'Agata | 95pts Vinum</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Camalaione</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Le Cinciole</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="7" t="n">
         <v>684</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="7" t="n">
         <v>684</v>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>Sob consulta</t>
         </is>
       </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Sem nota confirmada da safra 2018; safra 2019 recebeu 96pts Vinous e a 2020 recebeu 94+pts Vinous</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Volnay</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Chantal Lescure</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G23" s="7" t="n">
         <v>690</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H23" s="7" t="n">
         <v>690</v>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>Estoque Tanyno: 15un</t>
         </is>
       </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>Sem pontuacao/premiacao encontrada</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Le Marquis de Calon Segur</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Calon Segur</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="7" t="n">
         <v>694</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="7" t="n">
         <v>694</v>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>Sob consulta</t>
         </is>
       </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>91pts James Suckling | 92pts Vinous | 90pts Robert Parker/Wine Advocate | 16/20 Jancis Robinson</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Bourgogne Rouge</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>Domaine de Montille</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G25" s="8" t="n">
+      <c r="G25" s="10" t="n">
         <v>603.45</v>
       </c>
-      <c r="H25" s="8" t="n">
+      <c r="H25" s="10" t="n">
         <v>603.45</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>Borgonha - Pinot Noir</t>
         </is>
       </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>Sem nota individual de critico nomeado; media agregada Wine-Searcher ~87-88pts</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Chateau Fourcas Hosten (Listrac-Medoc)</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Cru Bourgeois</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G26" s="8" t="n">
+      <c r="G26" s="10" t="n">
         <v>605.1799999999999</v>
       </c>
-      <c r="H26" s="8" t="n">
+      <c r="H26" s="10" t="n">
         <v>605.1799999999999</v>
       </c>
-      <c r="I26" s="7" t="inlineStr"/>
+      <c r="I26" s="9" t="inlineStr"/>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>90pts James Suckling | 91pts Revue du Vin de France | 90pts Vinous (Neal Martin) | 87pts Wine Advocate</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Radici Taurasi DOCG</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Mastroberardino</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G27" s="8" t="n">
+      <c r="G27" s="10" t="n">
         <v>607.83</v>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="10" t="n">
         <v>607.83</v>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>Aglianico - Campania</t>
         </is>
       </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>94pts Vinous | 93pts James Suckling | 92pts Wine Spectator (Top 100 de 2022, posicao #84)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Barbera d'Alba DOC</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Bruno Giacosa</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G28" s="8" t="n">
+      <c r="G28" s="10" t="n">
         <v>622.37</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H28" s="10" t="n">
         <v>622.37</v>
       </c>
-      <c r="I28" s="7" t="inlineStr"/>
+      <c r="I28" s="9" t="inlineStr"/>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>Sem pontuacao/premiacao de critico nomeado (apenas media de comunidade CellarTracker ~90,7pts)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Domaine Alain Graillot Crozes-Hermitage AOC</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Alain Graillot</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G29" s="8" t="n">
+      <c r="G29" s="10" t="n">
         <v>622.37</v>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H29" s="10" t="n">
         <v>622.37</v>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>Rhone - Syrah</t>
         </is>
       </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>93pts Revue du Vin de France | 92pts Jeb Dunnuck | 92pts Vinous (Josh Raynolds) | 89-92pts Wine Advocate</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Cotes-du-Rhone Coudoulet de Beaucastel Rouge</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Chateau de Beaucastel</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G30" s="8" t="n">
+      <c r="G30" s="10" t="n">
         <v>633.73</v>
       </c>
-      <c r="H30" s="8" t="n">
+      <c r="H30" s="10" t="n">
         <v>633.73</v>
       </c>
-      <c r="I30" s="7" t="inlineStr"/>
+      <c r="I30" s="9" t="inlineStr"/>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>92pts Wine Advocate (Robert Parker) | 92pts James Suckling</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>Saint-Joseph Offerus</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Jean Louis Chave</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G31" s="8" t="n">
+      <c r="G31" s="10" t="n">
         <v>639.7</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H31" s="10" t="n">
         <v>639.7</v>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>Rhone - Syrah</t>
         </is>
       </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>92pts Wine Spectator | 91pts Jeb Dunnuck/Wine Advocate</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>Etna Rosso Santo Spirito</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Tenuta delle Terre Nere</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G32" s="8" t="n">
+      <c r="G32" s="10" t="n">
         <v>641.17</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="10" t="n">
         <v>641.17</v>
       </c>
-      <c r="I32" s="7" t="inlineStr"/>
+      <c r="I32" s="9" t="inlineStr"/>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>94pts Vinous | 94pts James Suckling | 93pts Wine Enthusiast | 91pts Wine Spectator</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Domaine de Villaine Bourgogne Cote Chalonnaise La Fortune</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>D. Aubert &amp; Pamela de Villaine</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="G33" s="10" t="n">
         <v>650.67</v>
       </c>
-      <c r="H33" s="8" t="n">
+      <c r="H33" s="10" t="n">
         <v>650.67</v>
       </c>
-      <c r="I33" s="7" t="inlineStr"/>
+      <c r="I33" s="9" t="inlineStr"/>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>Sem nota individual de critico nomeado; media agregada Wine-Searcher ~89pts</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>Rosso di Montalcino</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Andrea Costanti</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F34" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G34" s="10" t="n">
         <v>660.16</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="H34" s="10" t="n">
         <v>660.16</v>
       </c>
-      <c r="I34" s="7" t="inlineStr"/>
+      <c r="I34" s="9" t="inlineStr"/>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>Sem nota individual de critico nomeado; media agregada Wine-Searcher ~90pts</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>G D'Estournel (Medoc)</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>2o vinho do Cos D'Estournel</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G35" s="8" t="n">
+      <c r="G35" s="10" t="n">
         <v>673.89</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="10" t="n">
         <v>673.89</v>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>Mesmo rotulo do Site (comparar estoque)</t>
         </is>
       </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>93pts Vinous (Antonio Galloni) | ~92-93pts James Suckling | 91-93pts Decanter</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>Chateau Poujeaux (Medoc)</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Cru Bourgeois</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="G36" s="10" t="n">
         <v>680.3099999999999</v>
       </c>
-      <c r="H36" s="8" t="n">
+      <c r="H36" s="10" t="n">
         <v>680.3099999999999</v>
       </c>
-      <c r="I36" s="7" t="inlineStr"/>
+      <c r="I36" s="9" t="inlineStr"/>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>93pts James Suckling | 94pts Wine Enthusiast | 91pts Robert Parker/Wine Advocate | 91pts Decanter | 89pts Wine Spectator</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>Barolo Cellar Selection DOCG</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>Coppo</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G37" s="8" t="n">
+      <c r="G37" s="10" t="n">
         <v>686.59</v>
       </c>
-      <c r="H37" s="8" t="n">
+      <c r="H37" s="10" t="n">
         <v>686.59</v>
       </c>
-      <c r="I37" s="7" t="inlineStr"/>
+      <c r="I37" s="9" t="inlineStr"/>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>93pts Wine Enthusiast</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>Brunello di Montalcino</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Bonacchi</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G38" s="8" t="n">
+      <c r="G38" s="10" t="n">
         <v>686.59</v>
       </c>
-      <c r="H38" s="8" t="n">
+      <c r="H38" s="10" t="n">
         <v>686.59</v>
       </c>
-      <c r="I38" s="7" t="inlineStr"/>
+      <c r="I38" s="9" t="inlineStr"/>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>92pts Wine Enthusiast (Danielle Callegari)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>Domaine Faiveley Monthelie 1er Cru Les Duresses</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>Faiveley</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G39" s="10" t="n">
         <v>686.59</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="10" t="n">
         <v>686.59</v>
       </c>
-      <c r="I39" s="7" t="inlineStr"/>
+      <c r="I39" s="9" t="inlineStr"/>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>Sem nota numerica encontrada publicamente (reviews existem em Burghound/Vinous mas atras de paywall)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2034,854 +2246,964 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Barolo DOCG Sarmassa Vigna Merenda</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>Scarzello Giorgio</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="G41" s="7" t="n">
         <v>901</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="H41" s="7" t="n">
         <v>901</v>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>Estoque Tanyno: 14un</t>
         </is>
       </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>94pts Wine Enthusiast</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Morgon Passerelle 577</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>Mee Godard</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="G42" s="7" t="n">
         <v>914</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="H42" s="7" t="n">
         <v>914</v>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" s="6" t="inlineStr">
         <is>
           <t>Sob consulta</t>
         </is>
       </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>96pts James Suckling | 95pts Revue du Vin de France</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>Barbaresco DOCG Magnum</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>Giuseppe Cortese</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="G43" s="7" t="n">
         <v>920</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="H43" s="7" t="n">
         <v>920</v>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>Estoque Tanyno: 6un</t>
         </is>
       </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>94pts Vinous | 93pts Wine Spectator | 91pts Wine Enthusiast</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Brunello di Montalcino Nicco</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>Capanna</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="G44" s="7" t="n">
         <v>923</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="H44" s="7" t="n">
         <v>923</v>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>Estoque Tanyno: 12un</t>
         </is>
       </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>Sem nota numerica encontrada pra safra 2018 (James Suckling e Jancis Robinson tem reviews de 2016/2019/2021, atras de paywall)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Savigny-les-Beaune</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>Mongeard-Mugneret</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="G45" s="7" t="n">
         <v>949</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="H45" s="7" t="n">
         <v>949</v>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>Estoque Tanyno: 14un</t>
         </is>
       </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>94pts James Suckling e 93pts Wine Spectator (nota referente ao bottling 1er Cru Les Narbantons, mesmo produtor)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Cornas Chapelle Saint-Pierre</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>Domaine Alain Voge</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G46" s="6" t="n">
+      <c r="G46" s="7" t="n">
         <v>963</v>
       </c>
-      <c r="H46" s="6" t="n">
+      <c r="H46" s="7" t="n">
         <v>963</v>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I46" s="6" t="inlineStr">
         <is>
           <t>Estoque Tanyno: 14un</t>
         </is>
       </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>Sem nota numerica encontrada (Vinous tem review publicada, porem nota atras de paywall)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Cote Rotie Terrasses</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>Jean Luc Jamet</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>Tanyno</t>
         </is>
       </c>
-      <c r="G47" s="6" t="n">
+      <c r="G47" s="7" t="n">
         <v>988</v>
       </c>
-      <c r="H47" s="6" t="n">
+      <c r="H47" s="7" t="n">
         <v>988</v>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I47" s="6" t="inlineStr">
         <is>
           <t>Estoque Tanyno: 12un</t>
         </is>
       </c>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>93pts Robert Parker/The Wine Advocate</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="n">
+      <c r="A48" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>Chateau Barde Haut (Saint-Emilion Grand Cru Classe)</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>Ch. Barde Haut</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F48" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G48" s="8" t="n">
+      <c r="G48" s="10" t="n">
         <v>900.04</v>
       </c>
-      <c r="H48" s="8" t="n">
+      <c r="H48" s="10" t="n">
         <v>900.04</v>
       </c>
-      <c r="I48" s="7" t="inlineStr"/>
+      <c r="I48" s="9" t="inlineStr"/>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>~89pts media agregada Wine-Searcher (nao atribuida a critico especifico)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="n">
+      <c r="A49" s="9" t="n">
         <v>46</v>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>Savigny aux Grands Liards</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>Domaine Simon Bize</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D49" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F49" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G49" s="8" t="n">
+      <c r="G49" s="10" t="n">
         <v>903.0599999999999</v>
       </c>
-      <c r="H49" s="8" t="n">
+      <c r="H49" s="10" t="n">
         <v>903.0599999999999</v>
       </c>
-      <c r="I49" s="7" t="inlineStr"/>
+      <c r="I49" s="9" t="inlineStr"/>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>Sem nota exata da safra 2017; safra 2020 recebeu 90-92pts Wine Advocate (William Kelley) e 90-92pts Vinous (Neal Martin)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="n">
+      <c r="A50" s="9" t="n">
         <v>47</v>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>Tascante Contrada Pianodario Etna Rosso DOC</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>Tasca D'Almerita</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D50" s="9" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F50" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G50" s="8" t="n">
+      <c r="G50" s="10" t="n">
         <v>905.48</v>
       </c>
-      <c r="H50" s="8" t="n">
+      <c r="H50" s="10" t="n">
         <v>905.48</v>
       </c>
-      <c r="I50" s="7" t="inlineStr"/>
+      <c r="I50" s="9" t="inlineStr"/>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>96pts Falstaff | 93+pts Vinous (Eric Guido)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="n">
+      <c r="A51" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>Nebbiolo d'Alba Vigna Valmaggiore DOC</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>Bruno Giacosa</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G51" s="8" t="n">
+      <c r="G51" s="10" t="n">
         <v>905.51</v>
       </c>
-      <c r="H51" s="8" t="n">
+      <c r="H51" s="10" t="n">
         <v>905.51</v>
       </c>
-      <c r="I51" s="7" t="inlineStr"/>
+      <c r="I51" s="9" t="inlineStr"/>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>92pts Robert Parker/The Wine Advocate</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="n">
+      <c r="A52" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>Guidalberto</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>Tenuta San Guido</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="F52" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G52" s="8" t="n">
+      <c r="G52" s="10" t="n">
         <v>913.86</v>
       </c>
-      <c r="H52" s="8" t="n">
+      <c r="H52" s="10" t="n">
         <v>913.86</v>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="I52" s="9" t="inlineStr">
         <is>
           <t>Segundo vinho do Sassicaia</t>
         </is>
       </c>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>96pts James Suckling | 94pts Wine Enthusiast | 93pts Wine Advocate | 92pts Wine Spectator | 92pts Vinous</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="n">
+      <c r="A53" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>Chateau Cadet Bon (Saint-Emilion Grand Cru Classe)</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>Ch. Cadet Bon</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D53" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E53" s="9" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F53" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G53" s="8" t="n">
+      <c r="G53" s="10" t="n">
         <v>917.15</v>
       </c>
-      <c r="H53" s="8" t="n">
+      <c r="H53" s="10" t="n">
         <v>917.15</v>
       </c>
-      <c r="I53" s="7" t="inlineStr"/>
+      <c r="I53" s="9" t="inlineStr"/>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>Sem nota numerica de critico encontrada; recebeu 1 etoile no Guide Hachette des Vins (edicao 2012)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="n">
+      <c r="A54" s="9" t="n">
         <v>51</v>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>Mas de Daumas Gassac Rouge</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>Mas de Daumas Gassac</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="F54" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G54" s="8" t="n">
+      <c r="G54" s="10" t="n">
         <v>917.41</v>
       </c>
-      <c r="H54" s="8" t="n">
+      <c r="H54" s="10" t="n">
         <v>917.41</v>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="I54" s="9" t="inlineStr">
         <is>
           <t>Languedoc - cult wine</t>
         </is>
       </c>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>94pts Vinous (Neal Martin) | 94pts James Suckling | 92-94pts Robert Parker</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="n">
+      <c r="A55" s="9" t="n">
         <v>52</v>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>Chateau La Tour Carnet (Cru Classe Medoc)</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>Ch. La Tour Carnet</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D55" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F55" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G55" s="8" t="n">
+      <c r="G55" s="10" t="n">
         <v>923.6</v>
       </c>
-      <c r="H55" s="8" t="n">
+      <c r="H55" s="10" t="n">
         <v>923.6</v>
       </c>
-      <c r="I55" s="7" t="inlineStr"/>
+      <c r="I55" s="9" t="inlineStr"/>
+      <c r="J55" s="11" t="inlineStr">
+        <is>
+          <t>91pts Robert Parker/Wine Advocate</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="n">
+      <c r="A56" s="9" t="n">
         <v>53</v>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>Barolo DOCG Pressenda</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>Marziano Abbona</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E56" s="9" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr">
+      <c r="F56" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G56" s="8" t="n">
+      <c r="G56" s="10" t="n">
         <v>924.96</v>
       </c>
-      <c r="H56" s="8" t="n">
+      <c r="H56" s="10" t="n">
         <v>924.96</v>
       </c>
-      <c r="I56" s="7" t="inlineStr"/>
+      <c r="I56" s="9" t="inlineStr"/>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>Sem nota individual confirmada; media agregada Wine-Searcher ~93pts (Wine Spectator/James Suckling avaliaram mas nota ficou atras de paywall)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="n">
+      <c r="A57" s="9" t="n">
         <v>54</v>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>Chateau Kirwan (Cru Classe Margaux)</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>Ch. Kirwan</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D57" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E57" s="9" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="F57" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G57" s="8" t="n">
+      <c r="G57" s="10" t="n">
         <v>927.6</v>
       </c>
-      <c r="H57" s="8" t="n">
+      <c r="H57" s="10" t="n">
         <v>927.6</v>
       </c>
-      <c r="I57" s="7" t="inlineStr"/>
+      <c r="I57" s="9" t="inlineStr"/>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>Sem nota individual confirmada; media agregada Wine-Searcher ~88pts (safra 2013 considerada fraca em Bordeaux)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="n">
+      <c r="A58" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>Chateau Sociando-Mallet (Cru Bourgeois)</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>Ch. Sociando-Mallet</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D58" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
+      <c r="F58" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G58" s="8" t="n">
+      <c r="G58" s="10" t="n">
         <v>936.4</v>
       </c>
-      <c r="H58" s="8" t="n">
+      <c r="H58" s="10" t="n">
         <v>936.4</v>
       </c>
-      <c r="I58" s="7" t="inlineStr"/>
+      <c r="I58" s="9" t="inlineStr"/>
+      <c r="J58" s="11" t="inlineStr">
+        <is>
+          <t>93pts James Suckling</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="n">
+      <c r="A59" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>Chianti Classico Gran Selezione San Lorenzo</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>Castello di Ama</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D59" s="9" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E59" s="9" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="F59" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G59" s="8" t="n">
+      <c r="G59" s="10" t="n">
         <v>956.49</v>
       </c>
-      <c r="H59" s="8" t="n">
+      <c r="H59" s="10" t="n">
         <v>956.49</v>
       </c>
-      <c r="I59" s="7" t="inlineStr"/>
+      <c r="I59" s="9" t="inlineStr"/>
+      <c r="J59" s="11" t="inlineStr">
+        <is>
+          <t>95pts James Suckling | 95pts Vinous (Antonio Galloni) | 94pts Wine Spectator | 94pts Robert Parker</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="n">
+      <c r="A60" s="9" t="n">
         <v>57</v>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>Barolo DOCG</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>Coppo</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D60" s="9" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
+      <c r="F60" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G60" s="8" t="n">
+      <c r="G60" s="10" t="n">
         <v>964.6</v>
       </c>
-      <c r="H60" s="8" t="n">
+      <c r="H60" s="10" t="n">
         <v>964.6</v>
       </c>
-      <c r="I60" s="7" t="inlineStr"/>
+      <c r="I60" s="9" t="inlineStr"/>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>93pts Vinous | 91pts James Suckling</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="n">
+      <c r="A61" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>Chateau Les Ormes de Pez (Cru Bourgeois)</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>Ch. Les Ormes de Pez</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
+      <c r="F61" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G61" s="8" t="n">
+      <c r="G61" s="10" t="n">
         <v>968.49</v>
       </c>
-      <c r="H61" s="8" t="n">
+      <c r="H61" s="10" t="n">
         <v>968.49</v>
       </c>
-      <c r="I61" s="7" t="inlineStr"/>
+      <c r="I61" s="9" t="inlineStr"/>
+      <c r="J61" s="11" t="inlineStr">
+        <is>
+          <t>91pts Wine Enthusiast | 90pts Wine Spectator | 88pts James Suckling</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="n">
+      <c r="A62" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>Chateau Haut Bages Liberal (Cru Classe)</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t>Ch. Haut Bages Liberal</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D62" s="9" t="inlineStr">
         <is>
           <t>Franca</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F62" s="9" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="G62" s="8" t="n">
+      <c r="G62" s="10" t="n">
         <v>993.0700000000001</v>
       </c>
-      <c r="H62" s="8" t="n">
+      <c r="H62" s="10" t="n">
         <v>993.0700000000001</v>
       </c>
-      <c r="I62" s="7" t="inlineStr"/>
+      <c r="I62" s="9" t="inlineStr"/>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>90pts Robert Parker/Wine Advocate</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
@@ -2889,7 +3211,7 @@
           <t>Total se pegar TODOS da Faixa 1:</t>
         </is>
       </c>
-      <c r="G64" s="9" t="n">
+      <c r="G64" s="12" t="n">
         <v>24153.4</v>
       </c>
     </row>
@@ -2899,7 +3221,7 @@
           <t>Total se pegar TODOS da Faixa 2:</t>
         </is>
       </c>
-      <c r="G65" s="9" t="n">
+      <c r="G65" s="12" t="n">
         <v>20515.72</v>
       </c>
     </row>
@@ -2909,7 +3231,7 @@
           <t>Total geral (as duas faixas):</t>
         </is>
       </c>
-      <c r="G66" s="9" t="n">
+      <c r="G66" s="12" t="n">
         <v>44669.12</v>
       </c>
     </row>
@@ -2920,10 +3242,17 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Pontuacoes pesquisadas em: Wine Spectator, Robert Parker/Wine Advocate, James Suckling, Vinous, Decanter, Wine Enthusiast, Falstaff, Revue du Vin de France e guias (jul/2026). Quando a safra exata nao tinha nota publica, isso esta indicado no texto.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A40:I40"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
